--- a/data_logs/BenculukAgung.xlsx
+++ b/data_logs/BenculukAgung.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Activity Logs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +456,21 @@
           <t>Jumlah</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09 16:06:36</t>
+          <t>2026-10-10 11:33:28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>611673256</t>
+          <t>8343493744</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,39 +480,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ferry S Susanto</t>
+          <t>ferry.feva</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SUPERADMIN</t>
+          <t>USER_INPUT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>excasewa</t>
+          <t>aggra-kanan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>jam</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>sta0+5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10 08:28:21</t>
+          <t>2026-10-10 12:05:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8343493744</t>
+          <t>611673256</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -518,27 +527,267 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ferry.feva</t>
+          <t>Ferry S Susanto</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USER_INPUT</t>
+          <t>SUPERADMIN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[Edited] acbc-kanan</t>
+          <t>aggra-kanan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>sta0+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:07:53</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>aggra-kanan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>sta0+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:07:53</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>aggra-kanan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sta0+15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:07:53</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>aggra-kanan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>sta0+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:07:53</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>aggra-kanan</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sta0+25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:07:53</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>aggra-kanan</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>sta0+30</t>
         </is>
       </c>
     </row>

--- a/data_logs/BenculukAgung.xlsx
+++ b/data_logs/BenculukAgung.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,20 +443,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Keterangan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Satuan</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Jumlah</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
@@ -465,12 +470,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10 11:33:28</t>
+          <t>2026-10-12 12:24:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8343493744</t>
+          <t>611673256</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,39 +485,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ferry.feva</t>
+          <t>Ferry S Susanto</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USER_INPUT</t>
+          <t>SUPERADMIN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>acwc-kanan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sta0+5</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>sta0+50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:05:57</t>
+          <t>2026-10-12 12:26:02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,29 +547,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>acwc-kanan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sta0+10</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>sta0+150</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:07:53</t>
+          <t>2026-10-12 12:31:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -584,29 +599,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>acwc-kanan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>sta0+10</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sta0+250</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:07:53</t>
+          <t>2026-10-12 12:37:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,29 +651,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>acwc-kiri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>sta0+15</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sta0+50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:07:53</t>
+          <t>2026-10-12 12:37:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -678,29 +703,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>acwc-kiri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>sta0+20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>sta0+125</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10 12:07:53</t>
+          <t>2026-10-12 12:37:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -725,29 +755,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>acwc-kiri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>sta0+25</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sta0+250</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:07:53</t>
+          <t>2026-10-12 12:40:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -772,22 +807,79 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>aggra-kanan</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>acwc-kiri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>sta0+30</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>sta0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:40:05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>acwc-kiri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>sta0+150</t>
         </is>
       </c>
     </row>

--- a/data_logs/BenculukAgung.xlsx
+++ b/data_logs/BenculukAgung.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,266 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:42:24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>acwc-kiri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sta0+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:49:54</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1661996201</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>USER_ADMIN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>acwc-kiri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>coba</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:50:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1661996201</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>USER_ADMIN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>acwc-kiri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>coba</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:14:09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>acbc-kiri</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sta0+275</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>611673256</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ferry S Susanto</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>acbc-kiri</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>sta0+275</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
